--- a/Sindhi Muslim/Salary Sheet/Salary Sheet - November-2024.xlsx
+++ b/Sindhi Muslim/Salary Sheet/Salary Sheet - November-2024.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Salary Sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8B65718-FFF2-4CA6-91E6-B45280028B28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0586E741-2ED6-4660-A0FA-5FEDBE2D0E40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{92CE3A9B-E618-454F-A242-AE026DF5BDF3}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="10920" xr2:uid="{92CE3A9B-E618-454F-A242-AE026DF5BDF3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="87">
   <si>
     <t xml:space="preserve">Government High School Sindhi Jamaat Cooperative Housing Society, Bin Qasim Town Karachi </t>
   </si>
@@ -108,18 +108,6 @@
     <t>0003936568281601</t>
   </si>
   <si>
-    <t>Shehzana</t>
-  </si>
-  <si>
-    <t>Jamil Ur Rehman</t>
-  </si>
-  <si>
-    <t>42301-0658911-0</t>
-  </si>
-  <si>
-    <t>0003936570321601</t>
-  </si>
-  <si>
     <t>Tooba</t>
   </si>
   <si>
@@ -144,18 +132,6 @@
     <t>0003938883651001</t>
   </si>
   <si>
-    <t>Shahdab Kanwal</t>
-  </si>
-  <si>
-    <t>Ali Asghar</t>
-  </si>
-  <si>
-    <t>42501-1527894-9</t>
-  </si>
-  <si>
-    <t>0003939502581601</t>
-  </si>
-  <si>
     <t>Saba</t>
   </si>
   <si>
@@ -201,9 +177,6 @@
     <t>IT Teacher</t>
   </si>
   <si>
-    <t>42501-951762207</t>
-  </si>
-  <si>
     <t>01230104183142</t>
   </si>
   <si>
@@ -246,18 +219,9 @@
     <t>42501-5817372-7</t>
   </si>
   <si>
-    <t>Kazu</t>
-  </si>
-  <si>
-    <t>Yousuf Panwar</t>
-  </si>
-  <si>
     <t>Maid</t>
   </si>
   <si>
-    <t>41408 8263862 8</t>
-  </si>
-  <si>
     <t>Tahira Bibi</t>
   </si>
   <si>
@@ -286,6 +250,54 @@
   </si>
   <si>
     <t>Salary Sheet for the Month November 2024</t>
+  </si>
+  <si>
+    <t>Nusrat</t>
+  </si>
+  <si>
+    <t>Jhando Khan</t>
+  </si>
+  <si>
+    <t>41105-8110066-6</t>
+  </si>
+  <si>
+    <t>0003646014261000</t>
+  </si>
+  <si>
+    <t>0003936386121000</t>
+  </si>
+  <si>
+    <t>0003936299331000</t>
+  </si>
+  <si>
+    <t>Shumaila</t>
+  </si>
+  <si>
+    <t>42501-9517622-7</t>
+  </si>
+  <si>
+    <t>0003706594221001</t>
+  </si>
+  <si>
+    <t>Habib Ur Rehman</t>
+  </si>
+  <si>
+    <t>Montisory Director</t>
+  </si>
+  <si>
+    <t>42501-6502056-2</t>
+  </si>
+  <si>
+    <t>Uzma Sheraz</t>
+  </si>
+  <si>
+    <t>Sheraz Khan</t>
+  </si>
+  <si>
+    <t>Montisory Teacher</t>
+  </si>
+  <si>
+    <t>42401-1474395-4</t>
   </si>
 </sst>
 </file>
@@ -412,7 +424,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -694,137 +706,30 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -837,14 +742,10 @@
     <xf numFmtId="0" fontId="7" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -912,6 +813,138 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -919,7 +952,14 @@
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -971,43 +1011,6 @@
             <v>0</v>
           </cell>
           <cell r="AK5">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="AJ6">
-            <v>0</v>
-          </cell>
-          <cell r="AK6">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="AJ10">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="AJ11">
-            <v>0</v>
-          </cell>
-          <cell r="AK11">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="AJ12">
-            <v>0</v>
-          </cell>
-          <cell r="AK12">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="AJ13">
-            <v>0</v>
-          </cell>
-          <cell r="AK13">
             <v>0</v>
           </cell>
         </row>
@@ -1360,12 +1363,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F11A5F1A-9130-449F-92CE-1960C6A6F0AF}">
-  <dimension ref="A1:N31"/>
+  <dimension ref="A1:O31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18" bestFit="1" customWidth="1"/>
@@ -1377,1005 +1380,1002 @@
     <col min="12" max="12" width="5.85546875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11.140625" customWidth="1"/>
     <col min="14" max="14" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:15" ht="21" x14ac:dyDescent="0.25">
+      <c r="A1" s="39" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
+      <c r="L1" s="40"/>
+      <c r="M1" s="40"/>
+      <c r="N1" s="41"/>
+    </row>
+    <row r="2" spans="1:15" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="43"/>
+      <c r="J2" s="43"/>
+      <c r="K2" s="43"/>
+      <c r="L2" s="43"/>
+      <c r="M2" s="43"/>
+      <c r="N2" s="44"/>
+    </row>
+    <row r="3" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:15" ht="27" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="46"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="46"/>
+      <c r="H4" s="46"/>
+      <c r="I4" s="46"/>
+      <c r="J4" s="46"/>
+      <c r="K4" s="46"/>
+      <c r="L4" s="46"/>
+      <c r="M4" s="46"/>
+      <c r="N4" s="47"/>
+    </row>
+    <row r="5" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" s="48" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="51" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="51" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="51" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" s="54" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" s="54" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6" s="54" t="s">
+        <v>8</v>
+      </c>
+      <c r="H6" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="I6" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="J6" s="57"/>
+      <c r="K6" s="57"/>
+      <c r="L6" s="57"/>
+      <c r="M6" s="58" t="s">
+        <v>11</v>
+      </c>
+      <c r="N6" s="61" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" s="49"/>
+      <c r="B7" s="52"/>
+      <c r="C7" s="52"/>
+      <c r="D7" s="52"/>
+      <c r="E7" s="55"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="55"/>
+      <c r="H7" s="55"/>
+      <c r="I7" s="64" t="s">
+        <v>13</v>
+      </c>
+      <c r="J7" s="64" t="s">
+        <v>14</v>
+      </c>
+      <c r="K7" s="64" t="s">
+        <v>15</v>
+      </c>
+      <c r="L7" s="66" t="s">
+        <v>16</v>
+      </c>
+      <c r="M7" s="59"/>
+      <c r="N7" s="62"/>
+    </row>
+    <row r="8" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="50"/>
+      <c r="B8" s="53"/>
+      <c r="C8" s="53"/>
+      <c r="D8" s="53"/>
+      <c r="E8" s="56"/>
+      <c r="F8" s="53"/>
+      <c r="G8" s="56"/>
+      <c r="H8" s="56"/>
+      <c r="I8" s="65"/>
+      <c r="J8" s="65"/>
+      <c r="K8" s="65"/>
+      <c r="L8" s="67"/>
+      <c r="M8" s="60"/>
+      <c r="N8" s="63"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="28">
+        <v>44774</v>
+      </c>
+      <c r="F9" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="G9" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="H9" s="29">
+        <v>22000</v>
+      </c>
+      <c r="I9" s="15">
+        <v>30</v>
+      </c>
+      <c r="J9" s="15">
+        <v>24</v>
+      </c>
+      <c r="K9" s="15">
+        <v>6</v>
+      </c>
+      <c r="L9" s="15">
+        <f>[1]Attandance!AK5</f>
+        <v>0</v>
+      </c>
+      <c r="M9" s="15"/>
+      <c r="N9" s="16">
+        <v>17600</v>
+      </c>
+      <c r="O9" s="34"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="11">
+        <v>44774</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="H10" s="14">
+        <v>15000</v>
+      </c>
+      <c r="I10" s="10">
+        <v>30</v>
+      </c>
+      <c r="J10" s="15">
+        <v>24</v>
+      </c>
+      <c r="K10" s="10">
+        <v>6</v>
+      </c>
+      <c r="L10" s="10">
+        <v>0</v>
+      </c>
+      <c r="M10" s="10"/>
+      <c r="N10" s="35">
+        <v>12000</v>
+      </c>
+      <c r="O10" s="34"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="11">
+        <v>45198</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="G11" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="H11" s="14">
+        <v>15000</v>
+      </c>
+      <c r="I11" s="10">
+        <v>30</v>
+      </c>
+      <c r="J11" s="15">
+        <v>25</v>
+      </c>
+      <c r="K11" s="10">
+        <v>5</v>
+      </c>
+      <c r="L11" s="10">
+        <v>0</v>
+      </c>
+      <c r="M11" s="10"/>
+      <c r="N11" s="35">
+        <v>12500</v>
+      </c>
+      <c r="O11" s="34"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="11">
+        <v>45323</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="G12" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="H12" s="14">
+        <v>25000</v>
+      </c>
+      <c r="I12" s="10">
+        <v>30</v>
+      </c>
+      <c r="J12" s="10">
+        <v>28</v>
+      </c>
+      <c r="K12" s="10">
+        <v>2</v>
+      </c>
+      <c r="L12" s="10">
+        <v>0</v>
+      </c>
+      <c r="M12" s="10"/>
+      <c r="N12" s="35">
+        <v>23333.33</v>
+      </c>
+      <c r="O12" s="34"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E13" s="11">
+        <v>45536</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="G13" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="H13" s="14">
+        <v>20000</v>
+      </c>
+      <c r="I13" s="10">
+        <v>30</v>
+      </c>
+      <c r="J13" s="10">
+        <v>0</v>
+      </c>
+      <c r="K13" s="10">
+        <v>0</v>
+      </c>
+      <c r="L13" s="10">
+        <v>0</v>
+      </c>
+      <c r="M13" s="10"/>
+      <c r="N13" s="35">
+        <v>20000</v>
+      </c>
+      <c r="O13" s="34"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="11">
+        <v>45566</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="G14" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="H14" s="14">
+        <v>30000</v>
+      </c>
+      <c r="I14" s="10">
+        <v>30</v>
+      </c>
+      <c r="J14" s="10">
+        <v>0</v>
+      </c>
+      <c r="K14" s="10">
+        <v>0</v>
+      </c>
+      <c r="L14" s="10">
+        <v>0</v>
+      </c>
+      <c r="M14" s="10"/>
+      <c r="N14" s="35">
+        <v>30000</v>
+      </c>
+      <c r="O14" s="34"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="11">
+        <v>45597</v>
+      </c>
+      <c r="F15" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="3"/>
-    </row>
-    <row r="2" spans="1:14" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="6"/>
-    </row>
-    <row r="3" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
-      <c r="M4" s="8"/>
-      <c r="N4" s="9"/>
-    </row>
-    <row r="5" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="10"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
-      <c r="L5" s="10"/>
-      <c r="M5" s="10"/>
-      <c r="N5" s="10"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
+      <c r="G15" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="H15" s="14">
+        <v>30000</v>
+      </c>
+      <c r="I15" s="10">
+        <v>30</v>
+      </c>
+      <c r="J15" s="10">
+        <v>0</v>
+      </c>
+      <c r="K15" s="10">
+        <v>0</v>
+      </c>
+      <c r="L15" s="10">
+        <v>0</v>
+      </c>
+      <c r="M15" s="10"/>
+      <c r="N15" s="35">
+        <v>30000</v>
+      </c>
+      <c r="O15" s="34"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" s="79" t="s">
+        <v>83</v>
+      </c>
+      <c r="B16" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="11">
+        <v>45597</v>
+      </c>
+      <c r="F16" s="31" t="s">
+        <v>86</v>
+      </c>
+      <c r="G16" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="H16" s="14">
+        <v>26000</v>
+      </c>
+      <c r="I16" s="10">
+        <v>30</v>
+      </c>
+      <c r="J16" s="10">
+        <v>0</v>
+      </c>
+      <c r="K16" s="10">
+        <v>0</v>
+      </c>
+      <c r="L16" s="10">
+        <v>0</v>
+      </c>
+      <c r="M16" s="10"/>
+      <c r="N16" s="35">
+        <v>26000</v>
+      </c>
+      <c r="O16" s="34"/>
+    </row>
+    <row r="17" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="D17" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="19">
+        <v>45559</v>
+      </c>
+      <c r="F17" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="G17" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="H17" s="22">
+        <v>28000</v>
+      </c>
+      <c r="I17" s="18">
+        <v>30</v>
+      </c>
+      <c r="J17" s="18">
+        <v>0</v>
+      </c>
+      <c r="K17" s="18">
+        <v>0</v>
+      </c>
+      <c r="L17" s="18">
+        <v>0</v>
+      </c>
+      <c r="M17" s="24"/>
+      <c r="N17" s="36">
+        <v>28000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+    </row>
+    <row r="19" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+    </row>
+    <row r="20" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" s="46"/>
+      <c r="C20" s="46"/>
+      <c r="D20" s="46"/>
+      <c r="E20" s="46"/>
+      <c r="F20" s="46"/>
+      <c r="G20" s="46"/>
+      <c r="H20" s="46"/>
+      <c r="I20" s="46"/>
+      <c r="J20" s="46"/>
+      <c r="K20" s="46"/>
+      <c r="L20" s="46"/>
+      <c r="M20" s="46"/>
+      <c r="N20" s="47"/>
+    </row>
+    <row r="21" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B22" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C22" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D22" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E22" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="F22" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="14" t="s">
+      <c r="G22" s="68" t="s">
         <v>8</v>
       </c>
-      <c r="H6" s="14" t="s">
+      <c r="H22" s="68" t="s">
         <v>9</v>
       </c>
-      <c r="I6" s="15" t="s">
+      <c r="I22" s="71" t="s">
         <v>10</v>
       </c>
-      <c r="J6" s="15"/>
-      <c r="K6" s="15"/>
-      <c r="L6" s="15"/>
-      <c r="M6" s="16" t="s">
+      <c r="J22" s="71"/>
+      <c r="K22" s="71"/>
+      <c r="L22" s="71"/>
+      <c r="M22" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="N6" s="17" t="s">
+      <c r="N22" s="61" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="18"/>
-      <c r="B7" s="19"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="20"/>
-      <c r="H7" s="20"/>
-      <c r="I7" s="21" t="s">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A23" s="49"/>
+      <c r="B23" s="52"/>
+      <c r="C23" s="52"/>
+      <c r="D23" s="52"/>
+      <c r="E23" s="55"/>
+      <c r="F23" s="52"/>
+      <c r="G23" s="69"/>
+      <c r="H23" s="69"/>
+      <c r="I23" s="75" t="s">
         <v>13</v>
       </c>
-      <c r="J7" s="21" t="s">
+      <c r="J23" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="K7" s="21" t="s">
+      <c r="K23" s="75" t="s">
         <v>15</v>
       </c>
-      <c r="L7" s="22" t="s">
+      <c r="L23" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="M7" s="23"/>
-      <c r="N7" s="24"/>
-    </row>
-    <row r="8" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="25"/>
-      <c r="B8" s="26"/>
-      <c r="C8" s="26"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="27"/>
-      <c r="H8" s="27"/>
-      <c r="I8" s="28"/>
-      <c r="J8" s="28"/>
-      <c r="K8" s="28"/>
-      <c r="L8" s="29"/>
-      <c r="M8" s="30"/>
-      <c r="N8" s="31"/>
-    </row>
-    <row r="9" spans="1:14" s="50" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="43" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="44" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="44" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="44" t="s">
+      <c r="M23" s="73"/>
+      <c r="N23" s="62"/>
+    </row>
+    <row r="24" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="50"/>
+      <c r="B24" s="53"/>
+      <c r="C24" s="53"/>
+      <c r="D24" s="53"/>
+      <c r="E24" s="56"/>
+      <c r="F24" s="53"/>
+      <c r="G24" s="70"/>
+      <c r="H24" s="70"/>
+      <c r="I24" s="76"/>
+      <c r="J24" s="76"/>
+      <c r="K24" s="76"/>
+      <c r="L24" s="78"/>
+      <c r="M24" s="74"/>
+      <c r="N24" s="63"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D25" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="45">
-        <v>44774</v>
-      </c>
-      <c r="F9" s="46" t="s">
-        <v>21</v>
-      </c>
-      <c r="G9" s="47" t="s">
-        <v>22</v>
-      </c>
-      <c r="H9" s="48">
-        <v>22000</v>
-      </c>
-      <c r="I9" s="44">
+      <c r="E25" s="5">
+        <v>44475</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="G25" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="H25" s="7">
+        <v>60000</v>
+      </c>
+      <c r="I25" s="4">
         <v>30</v>
       </c>
-      <c r="J9" s="44">
-        <v>0</v>
-      </c>
-      <c r="K9" s="44">
-        <f>[1]Attandance!AJ5</f>
-        <v>0</v>
-      </c>
-      <c r="L9" s="44">
-        <f>[1]Attandance!AK5</f>
-        <v>0</v>
-      </c>
-      <c r="M9" s="44"/>
-      <c r="N9" s="49">
-        <v>22000</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" s="50" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="51" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="52" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" s="52" t="s">
+      <c r="J25" s="4">
+        <v>0</v>
+      </c>
+      <c r="K25" s="4">
+        <v>0</v>
+      </c>
+      <c r="L25" s="4">
+        <v>0</v>
+      </c>
+      <c r="M25" s="26">
+        <v>25000</v>
+      </c>
+      <c r="N25" s="8">
+        <v>85000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="D26" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="53">
-        <v>44774</v>
-      </c>
-      <c r="F10" s="54" t="s">
-        <v>25</v>
-      </c>
-      <c r="G10" s="55" t="s">
-        <v>26</v>
-      </c>
-      <c r="H10" s="56">
-        <v>18000</v>
-      </c>
-      <c r="I10" s="52">
+      <c r="E26" s="28">
+        <v>45468</v>
+      </c>
+      <c r="F26" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="G26" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="H26" s="29">
+        <v>24000</v>
+      </c>
+      <c r="I26" s="15">
         <v>30</v>
       </c>
-      <c r="J10" s="57">
-        <v>0</v>
-      </c>
-      <c r="K10" s="57">
-        <f>[1]Attandance!AJ6</f>
-        <v>0</v>
-      </c>
-      <c r="L10" s="57">
-        <f>[1]Attandance!AK6</f>
-        <v>0</v>
-      </c>
-      <c r="M10" s="52"/>
-      <c r="N10" s="58">
-        <v>18000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" s="50" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="51" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11" s="52" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="52" t="s">
+      <c r="J26" s="15">
+        <v>0</v>
+      </c>
+      <c r="K26" s="15">
+        <f>[1]Attandance!AJ20</f>
+        <v>0</v>
+      </c>
+      <c r="L26" s="15">
+        <f>[1]Attandance!AK20</f>
+        <v>0</v>
+      </c>
+      <c r="M26" s="15"/>
+      <c r="N26" s="16">
+        <v>24000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="D27" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="53">
-        <v>44774</v>
-      </c>
-      <c r="F11" s="54" t="s">
-        <v>29</v>
-      </c>
-      <c r="G11" s="55" t="s">
+      <c r="E27" s="28">
+        <v>45505</v>
+      </c>
+      <c r="F27" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="G27" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="H27" s="29">
+        <v>8000</v>
+      </c>
+      <c r="I27" s="15">
         <v>30</v>
       </c>
-      <c r="H11" s="56">
+      <c r="J27" s="15">
+        <v>0</v>
+      </c>
+      <c r="K27" s="15">
+        <f>[1]Attandance!AJ21</f>
+        <v>0</v>
+      </c>
+      <c r="L27" s="15">
+        <f>[1]Attandance!AK21</f>
+        <v>0</v>
+      </c>
+      <c r="M27" s="15"/>
+      <c r="N27" s="16">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28" s="27" t="s">
+        <v>71</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="D28" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="28">
+        <v>45597</v>
+      </c>
+      <c r="F28" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="G28" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="H28" s="29">
         <v>15000</v>
       </c>
-      <c r="I11" s="52">
+      <c r="I28" s="15">
         <v>30</v>
       </c>
-      <c r="J11" s="57">
-        <v>0</v>
-      </c>
-      <c r="K11" s="57">
-        <v>0</v>
-      </c>
-      <c r="L11" s="57">
-        <v>0</v>
-      </c>
-      <c r="M11" s="52"/>
-      <c r="N11" s="58">
+      <c r="J28" s="15">
+        <v>0</v>
+      </c>
+      <c r="K28" s="15">
+        <v>0</v>
+      </c>
+      <c r="L28" s="15">
+        <f>[1]Attandance!AK22</f>
+        <v>0</v>
+      </c>
+      <c r="M28" s="15"/>
+      <c r="N28" s="16">
         <v>15000</v>
       </c>
     </row>
-    <row r="12" spans="1:14" s="50" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="51" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="52" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="52" t="s">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A29" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="D29" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="53">
-        <v>45198</v>
-      </c>
-      <c r="F12" s="54" t="s">
-        <v>33</v>
-      </c>
-      <c r="G12" s="55" t="s">
-        <v>34</v>
-      </c>
-      <c r="H12" s="56">
+      <c r="E29" s="28">
+        <v>44967</v>
+      </c>
+      <c r="F29" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="G29" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="H29" s="29">
         <v>15000</v>
       </c>
-      <c r="I12" s="52">
+      <c r="I29" s="15">
         <v>30</v>
       </c>
-      <c r="J12" s="57">
-        <v>0</v>
-      </c>
-      <c r="K12" s="57">
-        <v>0</v>
-      </c>
-      <c r="L12" s="57">
-        <v>0</v>
-      </c>
-      <c r="M12" s="52"/>
-      <c r="N12" s="58">
+      <c r="J29" s="15">
+        <v>0</v>
+      </c>
+      <c r="K29" s="15">
+        <f>[1]Attandance!AJ23</f>
+        <v>0</v>
+      </c>
+      <c r="L29" s="15">
+        <f>[1]Attandance!AK23</f>
+        <v>0</v>
+      </c>
+      <c r="M29" s="15"/>
+      <c r="N29" s="16">
         <v>15000</v>
       </c>
     </row>
-    <row r="13" spans="1:14" s="50" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="51" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13" s="52" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" s="52" t="s">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="B30" s="30" t="s">
+        <v>65</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="D30" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="E13" s="53">
-        <v>45229</v>
-      </c>
-      <c r="F13" s="54" t="s">
-        <v>37</v>
-      </c>
-      <c r="G13" s="55" t="s">
+      <c r="E30" s="28">
+        <v>45587</v>
+      </c>
+      <c r="F30" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="G30" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="H13" s="56">
+      <c r="H30" s="29">
         <v>15000</v>
       </c>
-      <c r="I13" s="52">
+      <c r="I30" s="15">
         <v>30</v>
       </c>
-      <c r="J13" s="57">
-        <v>0</v>
-      </c>
-      <c r="K13" s="57">
-        <v>0</v>
-      </c>
-      <c r="L13" s="57">
-        <v>0</v>
-      </c>
-      <c r="M13" s="52"/>
-      <c r="N13" s="58">
+      <c r="J30" s="15">
+        <v>0</v>
+      </c>
+      <c r="K30" s="15">
+        <f>[1]Attandance!AJ24</f>
+        <v>0</v>
+      </c>
+      <c r="L30" s="15">
+        <f>[1]Attandance!AK24</f>
+        <v>0</v>
+      </c>
+      <c r="M30" s="10"/>
+      <c r="N30" s="16">
         <v>15000</v>
       </c>
     </row>
-    <row r="14" spans="1:14" s="50" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="51" t="s">
-        <v>39</v>
-      </c>
-      <c r="B14" s="52" t="s">
-        <v>40</v>
-      </c>
-      <c r="C14" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="D14" s="52" t="s">
+    <row r="31" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="B31" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="C31" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="D31" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E14" s="53">
-        <v>45323</v>
-      </c>
-      <c r="F14" s="54" t="s">
-        <v>41</v>
-      </c>
-      <c r="G14" s="55" t="s">
-        <v>42</v>
-      </c>
-      <c r="H14" s="56">
-        <v>25000</v>
-      </c>
-      <c r="I14" s="52">
+      <c r="E31" s="19">
+        <v>44959</v>
+      </c>
+      <c r="F31" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="G31" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="H31" s="33">
+        <v>15000</v>
+      </c>
+      <c r="I31" s="23">
         <v>30</v>
       </c>
-      <c r="J14" s="57">
-        <v>0</v>
-      </c>
-      <c r="K14" s="57">
-        <f>[1]Attandance!AJ10</f>
-        <v>0</v>
-      </c>
-      <c r="L14" s="57">
-        <v>0</v>
-      </c>
-      <c r="M14" s="52"/>
-      <c r="N14" s="58">
-        <v>25000</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" s="50" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="51" t="s">
-        <v>43</v>
-      </c>
-      <c r="B15" s="52" t="s">
-        <v>44</v>
-      </c>
-      <c r="C15" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="D15" s="52" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="53">
-        <v>45536</v>
-      </c>
-      <c r="F15" s="54" t="s">
-        <v>45</v>
-      </c>
-      <c r="G15" s="55" t="s">
-        <v>46</v>
-      </c>
-      <c r="H15" s="56">
-        <v>20000</v>
-      </c>
-      <c r="I15" s="52">
-        <v>30</v>
-      </c>
-      <c r="J15" s="57">
-        <v>0</v>
-      </c>
-      <c r="K15" s="57">
-        <f>[1]Attandance!AJ11</f>
-        <v>0</v>
-      </c>
-      <c r="L15" s="57">
-        <f>[1]Attandance!AK11</f>
-        <v>0</v>
-      </c>
-      <c r="M15" s="52"/>
-      <c r="N15" s="58">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" s="50" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="51" t="s">
-        <v>47</v>
-      </c>
-      <c r="B16" s="52" t="s">
-        <v>48</v>
-      </c>
-      <c r="C16" s="52" t="s">
-        <v>49</v>
-      </c>
-      <c r="D16" s="52" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="53">
-        <v>45566</v>
-      </c>
-      <c r="F16" s="54" t="s">
-        <v>50</v>
-      </c>
-      <c r="G16" s="55" t="s">
-        <v>46</v>
-      </c>
-      <c r="H16" s="56">
-        <v>30000</v>
-      </c>
-      <c r="I16" s="52">
-        <v>30</v>
-      </c>
-      <c r="J16" s="57">
-        <v>0</v>
-      </c>
-      <c r="K16" s="57">
-        <f>[1]Attandance!AJ12</f>
-        <v>0</v>
-      </c>
-      <c r="L16" s="57">
-        <f>[1]Attandance!AK12</f>
-        <v>0</v>
-      </c>
-      <c r="M16" s="52"/>
-      <c r="N16" s="58">
-        <v>30000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" s="50" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="59" t="s">
-        <v>51</v>
-      </c>
-      <c r="B17" s="60" t="s">
-        <v>52</v>
-      </c>
-      <c r="C17" s="60" t="s">
-        <v>53</v>
-      </c>
-      <c r="D17" s="60" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="61">
-        <v>45559</v>
-      </c>
-      <c r="F17" s="62" t="s">
-        <v>54</v>
-      </c>
-      <c r="G17" s="63" t="s">
-        <v>55</v>
-      </c>
-      <c r="H17" s="64">
-        <v>28000</v>
-      </c>
-      <c r="I17" s="60">
-        <v>30</v>
-      </c>
-      <c r="J17" s="65">
-        <v>0</v>
-      </c>
-      <c r="K17" s="65">
-        <f>[1]Attandance!AJ13</f>
-        <v>0</v>
-      </c>
-      <c r="L17" s="65">
-        <f>[1]Attandance!AK13</f>
-        <v>0</v>
-      </c>
-      <c r="M17" s="66"/>
-      <c r="N17" s="67">
-        <v>28000</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="10"/>
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
-      <c r="I18" s="10"/>
-      <c r="J18" s="10"/>
-      <c r="K18" s="10"/>
-      <c r="L18" s="10"/>
-      <c r="M18" s="10"/>
-      <c r="N18" s="10"/>
-    </row>
-    <row r="19" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="10"/>
-      <c r="B19" s="10"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="10"/>
-      <c r="I19" s="10"/>
-      <c r="J19" s="10"/>
-      <c r="K19" s="10"/>
-      <c r="L19" s="10"/>
-      <c r="M19" s="10"/>
-      <c r="N19" s="10"/>
-    </row>
-    <row r="20" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="8"/>
-      <c r="J20" s="8"/>
-      <c r="K20" s="8"/>
-      <c r="L20" s="8"/>
-      <c r="M20" s="8"/>
-      <c r="N20" s="9"/>
-    </row>
-    <row r="21" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="10"/>
-      <c r="B21" s="10"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="10"/>
-      <c r="I21" s="10"/>
-      <c r="J21" s="10"/>
-      <c r="K21" s="10"/>
-      <c r="L21" s="10"/>
-      <c r="M21" s="10"/>
-      <c r="N21" s="10"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="B22" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="C22" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="E22" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F22" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="G22" s="32" t="s">
-        <v>8</v>
-      </c>
-      <c r="H22" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="I22" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="J22" s="33"/>
-      <c r="K22" s="33"/>
-      <c r="L22" s="33"/>
-      <c r="M22" s="34" t="s">
-        <v>11</v>
-      </c>
-      <c r="N22" s="17" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="18"/>
-      <c r="B23" s="19"/>
-      <c r="C23" s="19"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="19"/>
-      <c r="G23" s="35"/>
-      <c r="H23" s="35"/>
-      <c r="I23" s="36" t="s">
-        <v>13</v>
-      </c>
-      <c r="J23" s="36" t="s">
-        <v>14</v>
-      </c>
-      <c r="K23" s="36" t="s">
-        <v>15</v>
-      </c>
-      <c r="L23" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="M23" s="38"/>
-      <c r="N23" s="24"/>
-    </row>
-    <row r="24" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="25"/>
-      <c r="B24" s="26"/>
-      <c r="C24" s="26"/>
-      <c r="D24" s="26"/>
-      <c r="E24" s="27"/>
-      <c r="F24" s="26"/>
-      <c r="G24" s="39"/>
-      <c r="H24" s="39"/>
-      <c r="I24" s="40"/>
-      <c r="J24" s="40"/>
-      <c r="K24" s="40"/>
-      <c r="L24" s="41"/>
-      <c r="M24" s="42"/>
-      <c r="N24" s="31"/>
-    </row>
-    <row r="25" spans="1:14" s="50" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="B25" s="44" t="s">
-        <v>58</v>
-      </c>
-      <c r="C25" s="44" t="s">
-        <v>59</v>
-      </c>
-      <c r="D25" s="44" t="s">
-        <v>20</v>
-      </c>
-      <c r="E25" s="45">
-        <v>44475</v>
-      </c>
-      <c r="F25" s="46" t="s">
-        <v>60</v>
-      </c>
-      <c r="G25" s="47" t="s">
-        <v>22</v>
-      </c>
-      <c r="H25" s="48">
-        <v>60000</v>
-      </c>
-      <c r="I25" s="44">
-        <v>30</v>
-      </c>
-      <c r="J25" s="44">
-        <v>0</v>
-      </c>
-      <c r="K25" s="44">
-        <v>0</v>
-      </c>
-      <c r="L25" s="44">
-        <v>0</v>
-      </c>
-      <c r="M25" s="68">
-        <v>25000</v>
-      </c>
-      <c r="N25" s="49">
-        <v>85000</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" s="50" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="69" t="s">
-        <v>61</v>
-      </c>
-      <c r="B26" s="52" t="s">
-        <v>62</v>
-      </c>
-      <c r="C26" s="57" t="s">
-        <v>63</v>
-      </c>
-      <c r="D26" s="57" t="s">
-        <v>20</v>
-      </c>
-      <c r="E26" s="70">
-        <v>45468</v>
-      </c>
-      <c r="F26" s="54" t="s">
-        <v>64</v>
-      </c>
-      <c r="G26" s="55" t="s">
-        <v>26</v>
-      </c>
-      <c r="H26" s="71">
-        <v>24000</v>
-      </c>
-      <c r="I26" s="57">
-        <v>30</v>
-      </c>
-      <c r="J26" s="57">
-        <v>0</v>
-      </c>
-      <c r="K26" s="57">
-        <f>[1]Attandance!AJ20</f>
-        <v>0</v>
-      </c>
-      <c r="L26" s="57">
-        <f>[1]Attandance!AK20</f>
-        <v>0</v>
-      </c>
-      <c r="M26" s="57"/>
-      <c r="N26" s="58">
-        <v>24000</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" s="50" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="69" t="s">
-        <v>65</v>
-      </c>
-      <c r="B27" s="52" t="s">
-        <v>66</v>
-      </c>
-      <c r="C27" s="57" t="s">
-        <v>67</v>
-      </c>
-      <c r="D27" s="57" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="70">
-        <v>45505</v>
-      </c>
-      <c r="F27" s="54" t="s">
-        <v>68</v>
-      </c>
-      <c r="G27" s="55" t="s">
-        <v>30</v>
-      </c>
-      <c r="H27" s="71">
-        <v>8000</v>
-      </c>
-      <c r="I27" s="57">
-        <v>30</v>
-      </c>
-      <c r="J27" s="57">
-        <v>0</v>
-      </c>
-      <c r="K27" s="57">
-        <f>[1]Attandance!AJ21</f>
-        <v>0</v>
-      </c>
-      <c r="L27" s="57">
-        <f>[1]Attandance!AK21</f>
-        <v>0</v>
-      </c>
-      <c r="M27" s="57"/>
-      <c r="N27" s="58">
-        <v>8000</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" s="50" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="69" t="s">
-        <v>69</v>
-      </c>
-      <c r="B28" s="52" t="s">
-        <v>70</v>
-      </c>
-      <c r="C28" s="57" t="s">
-        <v>71</v>
-      </c>
-      <c r="D28" s="57" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="70">
-        <v>44743</v>
-      </c>
-      <c r="F28" s="54" t="s">
-        <v>72</v>
-      </c>
-      <c r="G28" s="55" t="s">
-        <v>34</v>
-      </c>
-      <c r="H28" s="71">
-        <v>15000</v>
-      </c>
-      <c r="I28" s="57">
-        <v>30</v>
-      </c>
-      <c r="J28" s="57">
-        <v>0</v>
-      </c>
-      <c r="K28" s="57">
-        <v>0</v>
-      </c>
-      <c r="L28" s="57">
-        <f>[1]Attandance!AK22</f>
-        <v>0</v>
-      </c>
-      <c r="M28" s="57"/>
-      <c r="N28" s="58">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" s="50" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="69" t="s">
-        <v>73</v>
-      </c>
-      <c r="B29" s="52" t="s">
-        <v>74</v>
-      </c>
-      <c r="C29" s="57" t="s">
-        <v>71</v>
-      </c>
-      <c r="D29" s="57" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="70">
-        <v>44967</v>
-      </c>
-      <c r="F29" s="54" t="s">
-        <v>75</v>
-      </c>
-      <c r="G29" s="55" t="s">
-        <v>46</v>
-      </c>
-      <c r="H29" s="71">
-        <v>15000</v>
-      </c>
-      <c r="I29" s="57">
-        <v>30</v>
-      </c>
-      <c r="J29" s="57">
-        <v>0</v>
-      </c>
-      <c r="K29" s="57">
-        <f>[1]Attandance!AJ23</f>
-        <v>0</v>
-      </c>
-      <c r="L29" s="57">
-        <f>[1]Attandance!AK23</f>
-        <v>0</v>
-      </c>
-      <c r="M29" s="57"/>
-      <c r="N29" s="58">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" s="50" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="69" t="s">
-        <v>76</v>
-      </c>
-      <c r="B30" s="72" t="s">
-        <v>77</v>
-      </c>
-      <c r="C30" s="57" t="s">
-        <v>71</v>
-      </c>
-      <c r="D30" s="57" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="70">
-        <v>45587</v>
-      </c>
-      <c r="F30" s="73" t="s">
-        <v>78</v>
-      </c>
-      <c r="G30" s="74" t="s">
-        <v>46</v>
-      </c>
-      <c r="H30" s="71">
-        <v>15000</v>
-      </c>
-      <c r="I30" s="57">
-        <v>30</v>
-      </c>
-      <c r="J30" s="57">
-        <v>0</v>
-      </c>
-      <c r="K30" s="57">
-        <f>[1]Attandance!AJ24</f>
-        <v>0</v>
-      </c>
-      <c r="L30" s="57">
-        <f>[1]Attandance!AK24</f>
-        <v>0</v>
-      </c>
-      <c r="M30" s="52"/>
-      <c r="N30" s="58">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" s="50" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="59" t="s">
-        <v>79</v>
-      </c>
-      <c r="B31" s="60" t="s">
-        <v>74</v>
-      </c>
-      <c r="C31" s="65" t="s">
-        <v>80</v>
-      </c>
-      <c r="D31" s="65" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="61">
-        <v>44959</v>
-      </c>
-      <c r="F31" s="62" t="s">
-        <v>81</v>
-      </c>
-      <c r="G31" s="63" t="s">
-        <v>46</v>
-      </c>
-      <c r="H31" s="75">
-        <v>15000</v>
-      </c>
-      <c r="I31" s="65">
-        <v>30</v>
-      </c>
-      <c r="J31" s="65">
-        <v>0</v>
-      </c>
-      <c r="K31" s="65">
+      <c r="J31" s="23">
+        <v>0</v>
+      </c>
+      <c r="K31" s="23">
         <f>[1]Attandance!AJ25</f>
         <v>0</v>
       </c>
-      <c r="L31" s="65">
+      <c r="L31" s="23">
         <f>[1]Attandance!AK25</f>
         <v>0</v>
       </c>
-      <c r="M31" s="65"/>
-      <c r="N31" s="67">
+      <c r="M31" s="23"/>
+      <c r="N31" s="25">
         <v>15000</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="M22:M24"/>
-    <mergeCell ref="N22:N24"/>
-    <mergeCell ref="I23:I24"/>
-    <mergeCell ref="J23:J24"/>
     <mergeCell ref="K23:K24"/>
     <mergeCell ref="L23:L24"/>
+    <mergeCell ref="K7:K8"/>
+    <mergeCell ref="L7:L8"/>
     <mergeCell ref="A20:N20"/>
     <mergeCell ref="A22:A24"/>
     <mergeCell ref="B22:B24"/>
@@ -2386,14 +2386,10 @@
     <mergeCell ref="G22:G24"/>
     <mergeCell ref="H22:H24"/>
     <mergeCell ref="I22:L22"/>
-    <mergeCell ref="H6:H8"/>
-    <mergeCell ref="I6:L6"/>
-    <mergeCell ref="M6:M8"/>
-    <mergeCell ref="N6:N8"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="K7:K8"/>
-    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="M22:M24"/>
+    <mergeCell ref="N22:N24"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="J23:J24"/>
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A4:N4"/>
@@ -2404,19 +2400,30 @@
     <mergeCell ref="E6:E8"/>
     <mergeCell ref="F6:F8"/>
     <mergeCell ref="G6:G8"/>
+    <mergeCell ref="H6:H8"/>
+    <mergeCell ref="I6:L6"/>
+    <mergeCell ref="M6:M8"/>
+    <mergeCell ref="N6:N8"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="J7:J8"/>
   </mergeCells>
-  <conditionalFormatting sqref="B9:M9 B10:C13 M10:M16 D10:L17 C14:C16 F25:F31 D26:E31 K26:M31 G31:J31 G26:I30">
-    <cfRule type="expression" dxfId="0" priority="3">
+  <conditionalFormatting sqref="B9:M9 B10:C11 F25:F31 G26:I30 D26:E31 K26:M31 G31:J31 C12:C16 M10:M16 D10:L17">
+    <cfRule type="expression" dxfId="3" priority="4">
       <formula>$C9=#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C25:C31">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="2" priority="2">
       <formula>$C25=#REF!</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D25:E25 G25:M25 B25:B30 J26:J30">
-    <cfRule type="expression" dxfId="1" priority="2">
+  <conditionalFormatting sqref="D25:E25 H25:M25 B25:B30 J26:J30">
+    <cfRule type="expression" dxfId="1" priority="3">
+      <formula>$C25=#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G25">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>$C25=#REF!</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Sindhi Muslim/Salary Sheet/Salary Sheet - November-2024.xlsx
+++ b/Sindhi Muslim/Salary Sheet/Salary Sheet - November-2024.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Salary Sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0586E741-2ED6-4660-A0FA-5FEDBE2D0E40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10E4B3B0-14FE-414E-969E-1E780EBD2E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="10920" xr2:uid="{92CE3A9B-E618-454F-A242-AE026DF5BDF3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{92CE3A9B-E618-454F-A242-AE026DF5BDF3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -249,9 +249,6 @@
     <t>31201 2460819 2</t>
   </si>
   <si>
-    <t>Salary Sheet for the Month November 2024</t>
-  </si>
-  <si>
     <t>Nusrat</t>
   </si>
   <si>
@@ -298,6 +295,9 @@
   </si>
   <si>
     <t>42401-1474395-4</t>
+  </si>
+  <si>
+    <t>Salary Sheet for the Month August 2023</t>
   </si>
 </sst>
 </file>
@@ -824,22 +824,31 @@
     <xf numFmtId="49" fontId="8" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -878,6 +887,54 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -889,77 +946,13 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="3">
     <dxf>
       <fill>
         <patternFill>
@@ -1384,59 +1377,59 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="39" t="s">
-        <v>70</v>
-      </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="40"/>
-      <c r="M1" s="40"/>
-      <c r="N1" s="41"/>
+      <c r="A1" s="70" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="71"/>
+      <c r="I1" s="71"/>
+      <c r="J1" s="71"/>
+      <c r="K1" s="71"/>
+      <c r="L1" s="71"/>
+      <c r="M1" s="71"/>
+      <c r="N1" s="72"/>
     </row>
     <row r="2" spans="1:15" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="42" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="43"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="43"/>
-      <c r="I2" s="43"/>
-      <c r="J2" s="43"/>
-      <c r="K2" s="43"/>
-      <c r="L2" s="43"/>
-      <c r="M2" s="43"/>
-      <c r="N2" s="44"/>
+      <c r="A2" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="74"/>
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="74"/>
+      <c r="I2" s="74"/>
+      <c r="J2" s="74"/>
+      <c r="K2" s="74"/>
+      <c r="L2" s="74"/>
+      <c r="M2" s="74"/>
+      <c r="N2" s="75"/>
     </row>
     <row r="3" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:15" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="45" t="s">
+      <c r="A4" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="46"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="46"/>
-      <c r="G4" s="46"/>
-      <c r="H4" s="46"/>
-      <c r="I4" s="46"/>
-      <c r="J4" s="46"/>
-      <c r="K4" s="46"/>
-      <c r="L4" s="46"/>
-      <c r="M4" s="46"/>
-      <c r="N4" s="47"/>
+      <c r="B4" s="49"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="49"/>
+      <c r="H4" s="49"/>
+      <c r="I4" s="49"/>
+      <c r="J4" s="49"/>
+      <c r="K4" s="49"/>
+      <c r="L4" s="49"/>
+      <c r="M4" s="49"/>
+      <c r="N4" s="50"/>
     </row>
     <row r="5" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
@@ -1455,82 +1448,82 @@
       <c r="N5" s="1"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="48" t="s">
+      <c r="A6" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="51" t="s">
+      <c r="B6" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="51" t="s">
+      <c r="C6" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="51" t="s">
+      <c r="D6" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="54" t="s">
+      <c r="E6" s="57" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="54" t="s">
+      <c r="F6" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="54" t="s">
+      <c r="G6" s="57" t="s">
         <v>8</v>
       </c>
-      <c r="H6" s="54" t="s">
+      <c r="H6" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="I6" s="57" t="s">
+      <c r="I6" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="J6" s="57"/>
-      <c r="K6" s="57"/>
-      <c r="L6" s="57"/>
-      <c r="M6" s="58" t="s">
+      <c r="J6" s="76"/>
+      <c r="K6" s="76"/>
+      <c r="L6" s="76"/>
+      <c r="M6" s="77" t="s">
         <v>11</v>
       </c>
-      <c r="N6" s="61" t="s">
+      <c r="N6" s="67" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="49"/>
-      <c r="B7" s="52"/>
-      <c r="C7" s="52"/>
-      <c r="D7" s="52"/>
-      <c r="E7" s="55"/>
-      <c r="F7" s="52"/>
-      <c r="G7" s="55"/>
-      <c r="H7" s="55"/>
-      <c r="I7" s="64" t="s">
+      <c r="A7" s="52"/>
+      <c r="B7" s="55"/>
+      <c r="C7" s="55"/>
+      <c r="D7" s="55"/>
+      <c r="E7" s="58"/>
+      <c r="F7" s="55"/>
+      <c r="G7" s="58"/>
+      <c r="H7" s="58"/>
+      <c r="I7" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="J7" s="64" t="s">
+      <c r="J7" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="K7" s="64" t="s">
+      <c r="K7" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="L7" s="66" t="s">
+      <c r="L7" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="M7" s="59"/>
-      <c r="N7" s="62"/>
+      <c r="M7" s="78"/>
+      <c r="N7" s="68"/>
     </row>
     <row r="8" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="50"/>
-      <c r="B8" s="53"/>
-      <c r="C8" s="53"/>
-      <c r="D8" s="53"/>
-      <c r="E8" s="56"/>
-      <c r="F8" s="53"/>
-      <c r="G8" s="56"/>
-      <c r="H8" s="56"/>
-      <c r="I8" s="65"/>
-      <c r="J8" s="65"/>
-      <c r="K8" s="65"/>
-      <c r="L8" s="67"/>
-      <c r="M8" s="60"/>
-      <c r="N8" s="63"/>
+      <c r="A8" s="53"/>
+      <c r="B8" s="56"/>
+      <c r="C8" s="56"/>
+      <c r="D8" s="56"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="56"/>
+      <c r="G8" s="59"/>
+      <c r="H8" s="59"/>
+      <c r="I8" s="45"/>
+      <c r="J8" s="45"/>
+      <c r="K8" s="45"/>
+      <c r="L8" s="47"/>
+      <c r="M8" s="79"/>
+      <c r="N8" s="69"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="27" t="s">
@@ -1793,13 +1786,13 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B15" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="C15" s="10" t="s">
         <v>80</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>81</v>
       </c>
       <c r="D15" s="10" t="s">
         <v>20</v>
@@ -1808,10 +1801,10 @@
         <v>45597</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G15" s="13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H15" s="14">
         <v>30000</v>
@@ -1835,14 +1828,14 @@
       <c r="O15" s="34"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="79" t="s">
+      <c r="A16" s="39" t="s">
+        <v>82</v>
+      </c>
+      <c r="B16" s="30" t="s">
         <v>83</v>
       </c>
-      <c r="B16" s="30" t="s">
+      <c r="C16" s="10" t="s">
         <v>84</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>85</v>
       </c>
       <c r="D16" s="10" t="s">
         <v>20</v>
@@ -1851,7 +1844,7 @@
         <v>45597</v>
       </c>
       <c r="F16" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G16" s="32" t="s">
         <v>38</v>
@@ -1894,7 +1887,7 @@
         <v>45559</v>
       </c>
       <c r="F17" s="20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G17" s="21" t="s">
         <v>46</v>
@@ -1952,22 +1945,22 @@
       <c r="N19" s="1"/>
     </row>
     <row r="20" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="45" t="s">
+      <c r="A20" s="48" t="s">
         <v>47</v>
       </c>
-      <c r="B20" s="46"/>
-      <c r="C20" s="46"/>
-      <c r="D20" s="46"/>
-      <c r="E20" s="46"/>
-      <c r="F20" s="46"/>
-      <c r="G20" s="46"/>
-      <c r="H20" s="46"/>
-      <c r="I20" s="46"/>
-      <c r="J20" s="46"/>
-      <c r="K20" s="46"/>
-      <c r="L20" s="46"/>
-      <c r="M20" s="46"/>
-      <c r="N20" s="47"/>
+      <c r="B20" s="49"/>
+      <c r="C20" s="49"/>
+      <c r="D20" s="49"/>
+      <c r="E20" s="49"/>
+      <c r="F20" s="49"/>
+      <c r="G20" s="49"/>
+      <c r="H20" s="49"/>
+      <c r="I20" s="49"/>
+      <c r="J20" s="49"/>
+      <c r="K20" s="49"/>
+      <c r="L20" s="49"/>
+      <c r="M20" s="49"/>
+      <c r="N20" s="50"/>
     </row>
     <row r="21" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
@@ -1986,82 +1979,82 @@
       <c r="N21" s="1"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="48" t="s">
+      <c r="A22" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="B22" s="51" t="s">
+      <c r="B22" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="C22" s="51" t="s">
+      <c r="C22" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="D22" s="51" t="s">
+      <c r="D22" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="E22" s="54" t="s">
+      <c r="E22" s="57" t="s">
         <v>6</v>
       </c>
-      <c r="F22" s="54" t="s">
+      <c r="F22" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="G22" s="68" t="s">
+      <c r="G22" s="60" t="s">
         <v>8</v>
       </c>
-      <c r="H22" s="68" t="s">
+      <c r="H22" s="60" t="s">
         <v>9</v>
       </c>
-      <c r="I22" s="71" t="s">
+      <c r="I22" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="J22" s="71"/>
-      <c r="K22" s="71"/>
-      <c r="L22" s="71"/>
-      <c r="M22" s="72" t="s">
+      <c r="J22" s="63"/>
+      <c r="K22" s="63"/>
+      <c r="L22" s="63"/>
+      <c r="M22" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="N22" s="61" t="s">
+      <c r="N22" s="67" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="49"/>
-      <c r="B23" s="52"/>
-      <c r="C23" s="52"/>
-      <c r="D23" s="52"/>
-      <c r="E23" s="55"/>
-      <c r="F23" s="52"/>
-      <c r="G23" s="69"/>
-      <c r="H23" s="69"/>
-      <c r="I23" s="75" t="s">
+      <c r="A23" s="52"/>
+      <c r="B23" s="55"/>
+      <c r="C23" s="55"/>
+      <c r="D23" s="55"/>
+      <c r="E23" s="58"/>
+      <c r="F23" s="55"/>
+      <c r="G23" s="61"/>
+      <c r="H23" s="61"/>
+      <c r="I23" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="J23" s="75" t="s">
+      <c r="J23" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="K23" s="75" t="s">
+      <c r="K23" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="L23" s="77" t="s">
+      <c r="L23" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="M23" s="73"/>
-      <c r="N23" s="62"/>
+      <c r="M23" s="65"/>
+      <c r="N23" s="68"/>
     </row>
     <row r="24" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="50"/>
-      <c r="B24" s="53"/>
-      <c r="C24" s="53"/>
-      <c r="D24" s="53"/>
-      <c r="E24" s="56"/>
-      <c r="F24" s="53"/>
-      <c r="G24" s="70"/>
-      <c r="H24" s="70"/>
-      <c r="I24" s="76"/>
-      <c r="J24" s="76"/>
-      <c r="K24" s="76"/>
-      <c r="L24" s="78"/>
-      <c r="M24" s="74"/>
-      <c r="N24" s="63"/>
+      <c r="A24" s="53"/>
+      <c r="B24" s="56"/>
+      <c r="C24" s="56"/>
+      <c r="D24" s="56"/>
+      <c r="E24" s="59"/>
+      <c r="F24" s="56"/>
+      <c r="G24" s="62"/>
+      <c r="H24" s="62"/>
+      <c r="I24" s="41"/>
+      <c r="J24" s="41"/>
+      <c r="K24" s="41"/>
+      <c r="L24" s="43"/>
+      <c r="M24" s="66"/>
+      <c r="N24" s="69"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
@@ -2083,7 +2076,7 @@
         <v>51</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H25" s="7">
         <v>60000</v>
@@ -2127,7 +2120,7 @@
         <v>55</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H26" s="29">
         <v>24000</v>
@@ -2171,7 +2164,7 @@
         <v>59</v>
       </c>
       <c r="G27" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H27" s="29">
         <v>8000</v>
@@ -2197,10 +2190,10 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="27" t="s">
+        <v>70</v>
+      </c>
+      <c r="B28" s="10" t="s">
         <v>71</v>
-      </c>
-      <c r="B28" s="10" t="s">
-        <v>72</v>
       </c>
       <c r="C28" s="15" t="s">
         <v>68</v>
@@ -2212,7 +2205,7 @@
         <v>45597</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G28" s="13" t="s">
         <v>38</v>
@@ -2372,6 +2365,24 @@
     </row>
   </sheetData>
   <mergeCells count="34">
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="J23:J24"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A4:N4"/>
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="G6:G8"/>
+    <mergeCell ref="H6:H8"/>
+    <mergeCell ref="I6:L6"/>
+    <mergeCell ref="M6:M8"/>
+    <mergeCell ref="N6:N8"/>
     <mergeCell ref="K23:K24"/>
     <mergeCell ref="L23:L24"/>
     <mergeCell ref="K7:K8"/>
@@ -2388,41 +2399,18 @@
     <mergeCell ref="I22:L22"/>
     <mergeCell ref="M22:M24"/>
     <mergeCell ref="N22:N24"/>
-    <mergeCell ref="I23:I24"/>
-    <mergeCell ref="J23:J24"/>
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="A2:N2"/>
-    <mergeCell ref="A4:N4"/>
-    <mergeCell ref="A6:A8"/>
-    <mergeCell ref="B6:B8"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="F6:F8"/>
-    <mergeCell ref="G6:G8"/>
-    <mergeCell ref="H6:H8"/>
-    <mergeCell ref="I6:L6"/>
-    <mergeCell ref="M6:M8"/>
-    <mergeCell ref="N6:N8"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="J7:J8"/>
   </mergeCells>
-  <conditionalFormatting sqref="B9:M9 B10:C11 F25:F31 G26:I30 D26:E31 K26:M31 G31:J31 C12:C16 M10:M16 D10:L17">
-    <cfRule type="expression" dxfId="3" priority="4">
+  <conditionalFormatting sqref="B25:B30">
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>$C25=#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B9:M9 B10:C11 M10:M16 D10:L17 C12:C16">
+    <cfRule type="expression" dxfId="1" priority="4">
       <formula>$C9=#REF!</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C25:C31">
-    <cfRule type="expression" dxfId="2" priority="2">
-      <formula>$C25=#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D25:E25 H25:M25 B25:B30 J26:J30">
-    <cfRule type="expression" dxfId="1" priority="3">
-      <formula>$C25=#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G25">
+  <conditionalFormatting sqref="C25:M31">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$C25=#REF!</formula>
     </cfRule>

--- a/Sindhi Muslim/Salary Sheet/Salary Sheet - November-2024.xlsx
+++ b/Sindhi Muslim/Salary Sheet/Salary Sheet - November-2024.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Salary Sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10E4B3B0-14FE-414E-969E-1E780EBD2E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BB2F764-5294-4D6B-AFA7-DF8CFC795003}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{92CE3A9B-E618-454F-A242-AE026DF5BDF3}"/>
   </bookViews>
@@ -827,28 +827,34 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -887,6 +893,39 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -906,45 +945,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1377,59 +1377,59 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="44" t="s">
         <v>86</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="71"/>
-      <c r="I1" s="71"/>
-      <c r="J1" s="71"/>
-      <c r="K1" s="71"/>
-      <c r="L1" s="71"/>
-      <c r="M1" s="71"/>
-      <c r="N1" s="72"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="45"/>
+      <c r="K1" s="45"/>
+      <c r="L1" s="45"/>
+      <c r="M1" s="45"/>
+      <c r="N1" s="46"/>
     </row>
     <row r="2" spans="1:15" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="74"/>
-      <c r="C2" s="74"/>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="74"/>
-      <c r="I2" s="74"/>
-      <c r="J2" s="74"/>
-      <c r="K2" s="74"/>
-      <c r="L2" s="74"/>
-      <c r="M2" s="74"/>
-      <c r="N2" s="75"/>
+      <c r="A2" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="48"/>
+      <c r="L2" s="48"/>
+      <c r="M2" s="48"/>
+      <c r="N2" s="49"/>
     </row>
     <row r="3" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:15" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="48" t="s">
+      <c r="A4" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="49"/>
-      <c r="C4" s="49"/>
-      <c r="D4" s="49"/>
-      <c r="E4" s="49"/>
-      <c r="F4" s="49"/>
-      <c r="G4" s="49"/>
-      <c r="H4" s="49"/>
-      <c r="I4" s="49"/>
-      <c r="J4" s="49"/>
-      <c r="K4" s="49"/>
-      <c r="L4" s="49"/>
-      <c r="M4" s="49"/>
-      <c r="N4" s="50"/>
+      <c r="B4" s="51"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="51"/>
+      <c r="L4" s="51"/>
+      <c r="M4" s="51"/>
+      <c r="N4" s="52"/>
     </row>
     <row r="5" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
@@ -1448,82 +1448,82 @@
       <c r="N5" s="1"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="53" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="54" t="s">
+      <c r="B6" s="56" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="54" t="s">
+      <c r="C6" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="54" t="s">
+      <c r="D6" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="57" t="s">
+      <c r="E6" s="59" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="57" t="s">
+      <c r="F6" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="57" t="s">
+      <c r="G6" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="H6" s="57" t="s">
+      <c r="H6" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="I6" s="76" t="s">
+      <c r="I6" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="J6" s="76"/>
-      <c r="K6" s="76"/>
-      <c r="L6" s="76"/>
-      <c r="M6" s="77" t="s">
+      <c r="J6" s="62"/>
+      <c r="K6" s="62"/>
+      <c r="L6" s="62"/>
+      <c r="M6" s="63" t="s">
         <v>11</v>
       </c>
-      <c r="N6" s="67" t="s">
+      <c r="N6" s="66" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="52"/>
-      <c r="B7" s="55"/>
-      <c r="C7" s="55"/>
-      <c r="D7" s="55"/>
-      <c r="E7" s="58"/>
-      <c r="F7" s="55"/>
-      <c r="G7" s="58"/>
-      <c r="H7" s="58"/>
-      <c r="I7" s="44" t="s">
+      <c r="A7" s="54"/>
+      <c r="B7" s="57"/>
+      <c r="C7" s="57"/>
+      <c r="D7" s="57"/>
+      <c r="E7" s="60"/>
+      <c r="F7" s="57"/>
+      <c r="G7" s="60"/>
+      <c r="H7" s="60"/>
+      <c r="I7" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="J7" s="44" t="s">
+      <c r="J7" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="K7" s="44" t="s">
+      <c r="K7" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="L7" s="46" t="s">
+      <c r="L7" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="M7" s="78"/>
-      <c r="N7" s="68"/>
+      <c r="M7" s="64"/>
+      <c r="N7" s="67"/>
     </row>
     <row r="8" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="53"/>
-      <c r="B8" s="56"/>
-      <c r="C8" s="56"/>
-      <c r="D8" s="56"/>
-      <c r="E8" s="59"/>
-      <c r="F8" s="56"/>
-      <c r="G8" s="59"/>
-      <c r="H8" s="59"/>
-      <c r="I8" s="45"/>
-      <c r="J8" s="45"/>
-      <c r="K8" s="45"/>
-      <c r="L8" s="47"/>
-      <c r="M8" s="79"/>
-      <c r="N8" s="69"/>
+      <c r="A8" s="55"/>
+      <c r="B8" s="58"/>
+      <c r="C8" s="58"/>
+      <c r="D8" s="58"/>
+      <c r="E8" s="61"/>
+      <c r="F8" s="58"/>
+      <c r="G8" s="61"/>
+      <c r="H8" s="61"/>
+      <c r="I8" s="41"/>
+      <c r="J8" s="41"/>
+      <c r="K8" s="41"/>
+      <c r="L8" s="72"/>
+      <c r="M8" s="65"/>
+      <c r="N8" s="68"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="27" t="s">
@@ -1945,22 +1945,22 @@
       <c r="N19" s="1"/>
     </row>
     <row r="20" spans="1:14" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="48" t="s">
+      <c r="A20" s="50" t="s">
         <v>47</v>
       </c>
-      <c r="B20" s="49"/>
-      <c r="C20" s="49"/>
-      <c r="D20" s="49"/>
-      <c r="E20" s="49"/>
-      <c r="F20" s="49"/>
-      <c r="G20" s="49"/>
-      <c r="H20" s="49"/>
-      <c r="I20" s="49"/>
-      <c r="J20" s="49"/>
-      <c r="K20" s="49"/>
-      <c r="L20" s="49"/>
-      <c r="M20" s="49"/>
-      <c r="N20" s="50"/>
+      <c r="B20" s="51"/>
+      <c r="C20" s="51"/>
+      <c r="D20" s="51"/>
+      <c r="E20" s="51"/>
+      <c r="F20" s="51"/>
+      <c r="G20" s="51"/>
+      <c r="H20" s="51"/>
+      <c r="I20" s="51"/>
+      <c r="J20" s="51"/>
+      <c r="K20" s="51"/>
+      <c r="L20" s="51"/>
+      <c r="M20" s="51"/>
+      <c r="N20" s="52"/>
     </row>
     <row r="21" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
@@ -1979,82 +1979,82 @@
       <c r="N21" s="1"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="51" t="s">
+      <c r="A22" s="53" t="s">
         <v>2</v>
       </c>
-      <c r="B22" s="54" t="s">
+      <c r="B22" s="56" t="s">
         <v>3</v>
       </c>
-      <c r="C22" s="54" t="s">
+      <c r="C22" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="D22" s="54" t="s">
+      <c r="D22" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="E22" s="57" t="s">
+      <c r="E22" s="59" t="s">
         <v>6</v>
       </c>
-      <c r="F22" s="57" t="s">
+      <c r="F22" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="G22" s="60" t="s">
+      <c r="G22" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="H22" s="60" t="s">
+      <c r="H22" s="73" t="s">
         <v>9</v>
       </c>
-      <c r="I22" s="63" t="s">
+      <c r="I22" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="J22" s="63"/>
-      <c r="K22" s="63"/>
-      <c r="L22" s="63"/>
-      <c r="M22" s="64" t="s">
+      <c r="J22" s="76"/>
+      <c r="K22" s="76"/>
+      <c r="L22" s="76"/>
+      <c r="M22" s="77" t="s">
         <v>11</v>
       </c>
-      <c r="N22" s="67" t="s">
+      <c r="N22" s="66" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="52"/>
-      <c r="B23" s="55"/>
-      <c r="C23" s="55"/>
-      <c r="D23" s="55"/>
-      <c r="E23" s="58"/>
-      <c r="F23" s="55"/>
-      <c r="G23" s="61"/>
-      <c r="H23" s="61"/>
-      <c r="I23" s="40" t="s">
+      <c r="A23" s="54"/>
+      <c r="B23" s="57"/>
+      <c r="C23" s="57"/>
+      <c r="D23" s="57"/>
+      <c r="E23" s="60"/>
+      <c r="F23" s="57"/>
+      <c r="G23" s="74"/>
+      <c r="H23" s="74"/>
+      <c r="I23" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="J23" s="40" t="s">
+      <c r="J23" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="K23" s="40" t="s">
+      <c r="K23" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="L23" s="42" t="s">
+      <c r="L23" s="69" t="s">
         <v>16</v>
       </c>
-      <c r="M23" s="65"/>
-      <c r="N23" s="68"/>
+      <c r="M23" s="78"/>
+      <c r="N23" s="67"/>
     </row>
     <row r="24" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="53"/>
-      <c r="B24" s="56"/>
-      <c r="C24" s="56"/>
-      <c r="D24" s="56"/>
-      <c r="E24" s="59"/>
-      <c r="F24" s="56"/>
-      <c r="G24" s="62"/>
-      <c r="H24" s="62"/>
-      <c r="I24" s="41"/>
-      <c r="J24" s="41"/>
-      <c r="K24" s="41"/>
-      <c r="L24" s="43"/>
-      <c r="M24" s="66"/>
-      <c r="N24" s="69"/>
+      <c r="A24" s="55"/>
+      <c r="B24" s="58"/>
+      <c r="C24" s="58"/>
+      <c r="D24" s="58"/>
+      <c r="E24" s="61"/>
+      <c r="F24" s="58"/>
+      <c r="G24" s="75"/>
+      <c r="H24" s="75"/>
+      <c r="I24" s="43"/>
+      <c r="J24" s="43"/>
+      <c r="K24" s="43"/>
+      <c r="L24" s="70"/>
+      <c r="M24" s="79"/>
+      <c r="N24" s="68"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
@@ -2365,6 +2365,24 @@
     </row>
   </sheetData>
   <mergeCells count="34">
+    <mergeCell ref="M22:M24"/>
+    <mergeCell ref="N22:N24"/>
+    <mergeCell ref="M6:M8"/>
+    <mergeCell ref="N6:N8"/>
+    <mergeCell ref="K23:K24"/>
+    <mergeCell ref="L23:L24"/>
+    <mergeCell ref="K7:K8"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="A20:N20"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="B22:B24"/>
+    <mergeCell ref="C22:C24"/>
+    <mergeCell ref="D22:D24"/>
+    <mergeCell ref="E22:E24"/>
+    <mergeCell ref="F22:F24"/>
+    <mergeCell ref="G22:G24"/>
+    <mergeCell ref="H22:H24"/>
+    <mergeCell ref="I22:L22"/>
     <mergeCell ref="I7:I8"/>
     <mergeCell ref="J7:J8"/>
     <mergeCell ref="I23:I24"/>
@@ -2381,24 +2399,6 @@
     <mergeCell ref="G6:G8"/>
     <mergeCell ref="H6:H8"/>
     <mergeCell ref="I6:L6"/>
-    <mergeCell ref="M6:M8"/>
-    <mergeCell ref="N6:N8"/>
-    <mergeCell ref="K23:K24"/>
-    <mergeCell ref="L23:L24"/>
-    <mergeCell ref="K7:K8"/>
-    <mergeCell ref="L7:L8"/>
-    <mergeCell ref="A20:N20"/>
-    <mergeCell ref="A22:A24"/>
-    <mergeCell ref="B22:B24"/>
-    <mergeCell ref="C22:C24"/>
-    <mergeCell ref="D22:D24"/>
-    <mergeCell ref="E22:E24"/>
-    <mergeCell ref="F22:F24"/>
-    <mergeCell ref="G22:G24"/>
-    <mergeCell ref="H22:H24"/>
-    <mergeCell ref="I22:L22"/>
-    <mergeCell ref="M22:M24"/>
-    <mergeCell ref="N22:N24"/>
   </mergeCells>
   <conditionalFormatting sqref="B25:B30">
     <cfRule type="expression" dxfId="2" priority="3">
